--- a/languages/pt/output/import/葡萄牙语专八精通.xlsx
+++ b/languages/pt/output/import/葡萄牙语专八精通.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>[kõ.de.koˈɾa(ʁ)] 装饰&lt;动&gt;</t>
+          <t>[kõ.de.koˈɾa(ʁ)] 授勋；授予勋章&lt;动&gt;</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>装饰</t>
+          <t>授勋；授予勋章</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>[is.pɾiˈmi(ʁ)] 快递&lt;动&gt;</t>
+          <t>[is.pɾiˈmi(ʁ)] 表达&lt;动&gt;</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>快递</t>
+          <t>表达</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>a.fo.ga.ˈmẽ.tʊ</t>
+          <t>/a.fo.ga.ˈmẽ.tʊ/</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>[ˈmu] 亩&lt;名&gt;</t>
+          <t>[ˈmu] 希腊字母μ；哞（牛叫声）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>亩</t>
+          <t>希腊字母μ；哞（牛叫声）</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>[ˈʒĩ.bu] 金博&lt;名&gt;</t>
+          <t>[/ˈʒĩ.bu/] 洋麻；红麻（一种纤维植物）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>金博</t>
+          <t>洋麻；红麻（一种纤维植物）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>des.pa.ˈʃa.dʊ</t>
+          <t>/des.pa.ˈʃa.dʊ/</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>[siˈɾuʁ.ʒi.ku] 外科手术&lt;形&gt;</t>
+          <t>[/siˈɾuʁ.ʒi.ku/] 外科的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>外科手术</t>
+          <t>外科的</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>[ˈpi.ʃɐ] 公鸡&lt;名&gt;</t>
+          <t>[ˈpi.ʃɐ] 阴茎（粗俗语）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>公鸡</t>
+          <t>阴茎（粗俗语）</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.laˈt͡ʃi.vu] 亲戚&lt;形&gt;</t>
+          <t>[ʁe.laˈt͡ʃi.vu] 相对的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>亲戚</t>
+          <t>相对的</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ˈpɔs.tɾaw.ma.tʃi.kʊ</t>
+          <t>/ˈpɔs.tɾaw.ma.tʃi.kʊ/</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>[buˈʁi.tu] 墨西哥卷饼&lt;名&gt;</t>
+          <t>[/buˈʁi.tu/] 小驴&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>墨西哥卷饼</t>
+          <t>小驴</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>[ˈpi.u] 窥视&lt;名&gt;</t>
+          <t>[ˈpi.u] 鸟叫声；啾啾声&lt;名&gt;</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>窥视</t>
+          <t>鸟叫声；啾啾声</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>[peˈka(ʁ)] 罪恶&lt;动&gt;</t>
+          <t>[peˈka(ʁ)] 犯罪；犯错&lt;动&gt;</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>罪恶</t>
+          <t>犯罪；犯错</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ko.le.si.o.na.ˈdox</t>
+          <t>/ko.le.si.o.na.ˈdox/</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>[os.peˈda(ʁ)] 主机&lt;动&gt;</t>
+          <t>[os.peˈda(ʁ)] 招待；留宿&lt;动&gt;</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>主机</t>
+          <t>招待；留宿</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>[ne.ˈga.də] 被拒绝&lt;名&gt;</t>
+          <t>[ne.ˈga.də] 被拒绝的&lt;形&gt;；否定的&lt;形&gt;（negar 的阴性过去分词）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ne.ˈga.də</t>
+          <t>/ne.ˈga.də/</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>被拒绝</t>
+          <t>被拒绝的&lt;形&gt;；否定的&lt;形&gt;（negar 的阴性过去分词）</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>xe.tʃi.ˈɾa.ɾãʊ̃</t>
+          <t>/xe.tʃi.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>ne.go.ˈsi.ʊ</t>
+          <t>/ne.go.ˈsi.ʊ/</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>[vo.miˈta.du] 呕吐了&lt;名&gt;</t>
+          <t>[/vo.miˈta.du/] 呕吐的&lt;形&gt;（vomitar 的过去分词）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>呕吐了</t>
+          <t>呕吐的&lt;形&gt;（vomitar 的过去分词）</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>[ˈsub.di.tu] 主题&lt;名&gt;</t>
+          <t>[ˈsub.di.tu] 臣民&lt;名&gt;</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>主题</t>
+          <t>臣民</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>[ɡo.veʁˈnɐ̃.t͡ʃi] 尺子&lt;名&gt;</t>
+          <t>[ɡo.veʁˈnɐ̃.t͡ʃi] 统治者；执政者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>尺子</t>
+          <t>统治者；执政者</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>[is.taˈla(ʁ)] 快照&lt;动&gt;</t>
+          <t>[is.taˈla(ʁ)] 发出爆裂声；折断；噼啪作响&lt;动&gt;</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>快照</t>
+          <t>发出爆裂声；折断；噼啪作响</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>[koˈmi.sju] 拉力赛&lt;名&gt;</t>
+          <t>[koˈmi.sju] 集会；群众大会&lt;名&gt;</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>拉力赛</t>
+          <t>集会；群众大会</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>[ˈvɛ.njɐ] 弓&lt;名&gt;</t>
+          <t>[ˈvɛ.njɐ] 鞠躬；颔首礼&lt;名&gt;</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>弓</t>
+          <t>鞠躬；颔首礼</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɔk.sɛɾʃ] 拳击手&lt;名&gt;</t>
+          <t>[/ˈbɔk.sɛɾʃ/] 拳击短裤；平角内裤&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>拳击手</t>
+          <t>拳击短裤；平角内裤&lt;名&gt;</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>[siˈlĩ.dɾu] 气缸&lt;名&gt;</t>
+          <t>[/siˈlĩ.dɾu/] 圆柱体；圆柱&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>气缸</t>
+          <t>圆柱体；圆柱&lt;名&gt;</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>mã.tʃi.ˈvɛ.ɾãʊ̃</t>
+          <t>/mã.tʃi.ˈvɛ.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
@@ -4246,7 +4246,11 @@
           <t>高尔夫&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr"/>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɡɑlf/</t>
+        </is>
+      </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
           <t>高尔夫</t>
@@ -4335,7 +4339,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>[ko.lo.niˈaw] 殖民地&lt;形&gt;</t>
+          <t>[ko.lo.niˈaw] 殖民的；殖民地的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4345,7 +4349,7 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>殖民地</t>
+          <t>殖民的；殖民地的</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -4564,7 +4568,7 @@
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>tɾo.ˈka.ɾãʊ̃</t>
+          <t>/tɾo.ˈka.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
@@ -4815,7 +4819,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒi.ʒeˈɾi(ʁ)] 摘要&lt;动&gt;</t>
+          <t>[d͡ʒi.ʒeˈɾi(ʁ)] 消化；领会&lt;动&gt;</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4825,7 +4829,7 @@
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>摘要</t>
+          <t>消化；领会</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4852,7 +4856,7 @@
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>de.ziʃ.ˈtʃi.ɾãʊ̃</t>
+          <t>/de.ziʃ.ˈtʃi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -4943,7 +4947,7 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>[meˈa.du] 中&lt;名&gt;</t>
+          <t>[meˈa.du] 中旬；中间部分&lt;名&gt;</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -4953,7 +4957,7 @@
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中旬；中间部分</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -5199,7 +5203,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>[ve.leˈʒa(ʁ)] 帆&lt;动&gt;</t>
+          <t>[ve.leˈʒa(ʁ)] 帆船航行；航行&lt;动&gt;</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -5209,7 +5213,7 @@
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>帆</t>
+          <t>帆船航行；航行</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -5295,7 +5299,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>[kõ.kɾe.t͡ʃiˈza(ʁ)] 意识到&lt;动&gt;</t>
+          <t>[kõ.kɾe.t͡ʃiˈza(ʁ)] 实现；落实；使具体化&lt;动&gt;</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -5305,7 +5309,7 @@
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>意识到</t>
+          <t>实现；落实；使具体化</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
@@ -6164,7 +6168,7 @@
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>fɾa.ˈsãʊ̃</t>
+          <t>/fɾa.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
@@ -6479,7 +6483,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>[a.bas.teˈse(ʁ)] 燃料&lt;动&gt;</t>
+          <t>[a.bas.teˈse(ʁ)] 供应；补给；加油&lt;动&gt;</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -6489,7 +6493,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>燃料</t>
+          <t>供应；补给；加油</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -7092,7 +7096,7 @@
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>xe.bẽ.ˈta.ɾãʊ̃</t>
+          <t>/xe.bẽ.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -7124,7 +7128,7 @@
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>ʒo.ˈga.ɾãʊ̃</t>
+          <t>/ʒo.ˈga.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -7375,17 +7379,17 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[pa.sa.ˈɾãʊ̃] 会过去的&lt;动&gt;</t>
+          <t>[pa.sa.ˈɾãʊ̃] 将通过；将过去；将度过&lt;动&gt;</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>pa.sa.ˈɾãʊ̃</t>
+          <t>/pa.sa.ˈɾãʊ̃/</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>会过去的</t>
+          <t>将通过；将过去；将度过</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -7407,7 +7411,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>[kaw.kɐ̃ˈɲaʁ] 鞋跟&lt;名&gt;</t>
+          <t>[/kaw.kɐ̃ˈɲaʁ/] 脚跟；足跟&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -7417,7 +7421,7 @@
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>鞋跟</t>
+          <t>脚跟；足跟</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -7922,7 +7926,11 @@
           <t>作弊&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C235" s="1" t="inlineStr"/>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>/tɾɐ̃ˈpa(ʁ)/</t>
+        </is>
+      </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
           <t>作弊</t>
@@ -8011,17 +8019,17 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃa] 查&lt;名&gt;</t>
+          <t>[ˈʃa] 茶&lt;名&gt;</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>ˈʃa</t>
+          <t>/ˈʃa/</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>查</t>
+          <t>茶</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
@@ -8110,10 +8118,14 @@
           <t>锤子&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C241" s="1" t="inlineStr"/>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>/ˈhæm.ɚ/</t>
+        </is>
+      </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t>锤子</t>
+          <t>英语词，非葡萄牙语词条</t>
         </is>
       </c>
       <c r="E241" s="1" t="inlineStr">
@@ -8268,7 +8280,7 @@
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>se.pa.ˈɾa.ɾãʊ̃</t>
+          <t>/se.pa.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
@@ -8295,7 +8307,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.baʁ.kaˈsɐ̃w̃] 容器&lt;名&gt;</t>
+          <t>[ẽ.baʁ.kaˈsɐ̃w̃] 船；船只&lt;名&gt;</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
@@ -8305,7 +8317,7 @@
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t>容器</t>
+          <t>船；船只</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
@@ -8492,7 +8504,7 @@
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t>es.pe.ˈɾa.ɾãʊ̃</t>
+          <t>/es.pe.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
@@ -8583,7 +8595,7 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>[aˈma.ʁɐ] 领带&lt;名&gt;</t>
+          <t>[aˈma.ʁɐ] 缆绳；系船索；束缚&lt;名&gt;</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
@@ -8593,7 +8605,7 @@
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t>领带</t>
+          <t>缆绳；系船索；束缚</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
@@ -8615,7 +8627,7 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>[desˈfej.tɐ] 未完成的&lt;名&gt;</t>
+          <t>[desˈfej.tɐ] 恶行；侮辱；伤害&lt;名&gt;</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
@@ -8625,7 +8637,7 @@
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t>未完成的</t>
+          <t>恶行；侮辱；伤害</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
@@ -9095,7 +9107,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>[ˈa.kɾi] 英亩&lt;名&gt;</t>
+          <t>[/ˈa.kɾi/] 辛辣的；刺鼻的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -9105,7 +9117,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>英亩</t>
+          <t>辛辣的；刺鼻的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
@@ -9196,7 +9208,7 @@
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>a.de.kwa.da.ˈmẽ.tʃɪ</t>
+          <t>/a.de.kwa.da.ˈmẽ.tʃɪ/</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -9223,17 +9235,17 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>[de.zẽ.vow.ˈve.ɾãʊ̃] 发达的&lt;动&gt;</t>
+          <t>[de.zẽ.vow.ˈve.ɾãʊ̃] 发展；开发&lt;动&gt;</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>de.zẽ.vow.ˈve.ɾãʊ̃</t>
+          <t>/de.zẽ.vow.ˈve.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>发达的</t>
+          <t>发展；开发</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
@@ -9319,7 +9331,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>[laˈmɛ.ʃɐs] 跛脚的&lt;形&gt;</t>
+          <t>[laˈmɛ.ʃɐs] 少量液体；一摊液体&lt;形&gt;</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -9329,7 +9341,7 @@
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>跛脚的</t>
+          <t>少量液体；一摊液体</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
@@ -9450,7 +9462,11 @@
           <t>日复一日&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C283" s="1" t="inlineStr"/>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>/di.ɐ.ɐˈdi.ɐ/</t>
+        </is>
+      </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
           <t>日复一日</t>
@@ -9699,7 +9715,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>[niˈna(ʁ)] 摇篮曲&lt;动&gt;</t>
+          <t>[niˈna(ʁ)] 哄（婴儿）入睡&lt;动&gt;</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -9709,7 +9725,7 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>摇篮曲</t>
+          <t>哄（婴儿）入睡</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
@@ -9731,7 +9747,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>[maʁˈke.zɐ] 沙发&lt;名&gt;</t>
+          <t>[maʁˈke.zɐ] 侯爵夫人；女侯爵&lt;名&gt;</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -9741,7 +9757,7 @@
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>沙发</t>
+          <t>侯爵夫人；女侯爵</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
@@ -9827,7 +9843,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>[naˈzaw] 鼻的&lt;名&gt;</t>
+          <t>[/naˈzaw/] 鼻的；鼻音的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -9837,7 +9853,7 @@
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t>鼻的</t>
+          <t>鼻的；鼻音的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
@@ -9896,7 +9912,7 @@
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>i.dẽ.tʃi.fi.ˈka.ɾãʊ̃</t>
+          <t>/i.dẽ.tʃi.fi.ˈka.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
@@ -10083,7 +10099,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>[a.tɾeˈla.du] 拖车&lt;名&gt;</t>
+          <t>[a.tɾeˈla.du] 拖车；挂车&lt;名&gt;</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
@@ -10093,7 +10109,7 @@
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t>拖车</t>
+          <t>拖车；挂车</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
@@ -10278,7 +10294,11 @@
           <t>环&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C309" s="1" t="inlineStr"/>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>/rɪŋ/</t>
+        </is>
+      </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
           <t>环</t>
@@ -10495,7 +10515,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[kõ.tesˈta(ʁ)] 竞赛&lt;动&gt;</t>
+          <t>[kõ.tesˈta(ʁ)] 质疑；反驳；对…提出异议&lt;动&gt;</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -10505,7 +10525,7 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t>竞赛</t>
+          <t>质疑；反驳；对…提出异议</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
@@ -10815,7 +10835,7 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>[ˈsow] 灵魂&lt;名&gt;</t>
+          <t>[/ˈsow/] 灵魂乐（一种音乐风格）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -10825,7 +10845,7 @@
       </c>
       <c r="D326" s="1" t="inlineStr">
         <is>
-          <t>灵魂</t>
+          <t>灵魂乐（一种音乐风格）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
@@ -10884,7 +10904,7 @@
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t>ˈa.tɾəs</t>
+          <t>/ˈa.tɾəs/</t>
         </is>
       </c>
       <c r="D328" s="1" t="inlineStr">
@@ -11074,7 +11094,11 @@
           <t>密码&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C334" s="1" t="inlineStr"/>
+      <c r="C334" s="1" t="inlineStr">
+        <is>
+          <t>/pa.ˈla.vɾɐ ˈpa.si/</t>
+        </is>
+      </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
           <t>密码</t>
@@ -11136,7 +11160,7 @@
       </c>
       <c r="C336" s="1" t="inlineStr">
         <is>
-          <t>pɾo.ˈva.ɾãʊ̃</t>
+          <t>/pɾo.ˈva.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D336" s="1" t="inlineStr">
@@ -11483,7 +11507,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>[kɾa.niˈɐ̃.nu] 颅骨&lt;形&gt;</t>
+          <t>[kɾa.niˈɐ̃.nu] 颅骨的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
@@ -11493,7 +11517,7 @@
       </c>
       <c r="D347" s="1" t="inlineStr">
         <is>
-          <t>颅骨</t>
+          <t>颅骨的</t>
         </is>
       </c>
       <c r="E347" s="1" t="inlineStr">
@@ -11579,7 +11603,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>[buˈd͡ʒis.tɐ] 佛教&lt;名&gt;</t>
+          <t>[buˈd͡ʒis.tɐ] 佛教的；佛教徒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
@@ -11589,7 +11613,7 @@
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t>佛教</t>
+          <t>佛教的；佛教徒</t>
         </is>
       </c>
       <c r="E350" s="1" t="inlineStr">
@@ -11771,7 +11795,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>[de.za.t͡ʃiˈva.du] 残疾人&lt;形&gt;</t>
+          <t>[de.za.t͡ʃiˈva.du] 已停用的；已解除的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
@@ -11781,7 +11805,7 @@
       </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
-          <t>残疾人</t>
+          <t>已停用的；已解除的</t>
         </is>
       </c>
       <c r="E356" s="1" t="inlineStr">
@@ -11966,7 +11990,11 @@
           <t>阿门&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C362" s="1" t="inlineStr"/>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>/ˈamen/</t>
+        </is>
+      </c>
       <c r="D362" s="1" t="inlineStr">
         <is>
           <t>阿门</t>
@@ -12028,7 +12056,7 @@
       </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t>xe.ku.ˈza.ɾãʊ̃</t>
+          <t>/xe.ku.ˈza.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D364" s="1" t="inlineStr">
@@ -12215,7 +12243,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>[a.maˈzõ.nɐ] 亚马逊&lt;名&gt;</t>
+          <t>[a.maˈzõ.nɐ] 女骑手；亚马逊女战士&lt;名&gt;</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
@@ -12225,7 +12253,7 @@
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t>亚马逊</t>
+          <t>女骑手；亚马逊女战士</t>
         </is>
       </c>
       <c r="E370" s="1" t="inlineStr">
@@ -12343,7 +12371,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡɔ.ɾi] 戈尔&lt;名&gt;</t>
+          <t>[ˈɡɔ.ɾi] 血腥；血腥暴力&lt;名&gt;</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
@@ -12353,7 +12381,7 @@
       </c>
       <c r="D374" s="1" t="inlineStr">
         <is>
-          <t>戈尔</t>
+          <t>血腥；血腥暴力</t>
         </is>
       </c>
       <c r="E374" s="1" t="inlineStr">
@@ -12410,7 +12438,11 @@
           <t>长曲棍球&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C376" s="1" t="inlineStr"/>
+      <c r="C376" s="1" t="inlineStr">
+        <is>
+          <t>/lakʁˈosse/</t>
+        </is>
+      </c>
       <c r="D376" s="1" t="inlineStr">
         <is>
           <t>长曲棍球</t>
@@ -12982,7 +13014,11 @@
           <t>说&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C394" s="1" t="inlineStr"/>
+      <c r="C394" s="1" t="inlineStr">
+        <is>
+          <t>/seɪ/</t>
+        </is>
+      </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
           <t>说</t>
@@ -13044,7 +13080,7 @@
       </c>
       <c r="C396" s="1" t="inlineStr">
         <is>
-          <t>six.ˈku.lʊ</t>
+          <t>/six.ˈku.lʊ/</t>
         </is>
       </c>
       <c r="D396" s="1" t="inlineStr">
@@ -13103,7 +13139,7 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>[a.peʁ.fej.soˈa(ʁ)] 完美的&lt;动&gt;</t>
+          <t>[a.peʁ.fej.soˈa(ʁ)] 完善；改进；使完美&lt;动&gt;</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
@@ -13113,7 +13149,7 @@
       </c>
       <c r="D398" s="1" t="inlineStr">
         <is>
-          <t>完美的</t>
+          <t>完善；改进；使完美</t>
         </is>
       </c>
       <c r="E398" s="1" t="inlineStr">
@@ -13295,7 +13331,7 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>[ˈʒẽ.mɐ] 宝石&lt;名&gt;</t>
+          <t>[ˈʒẽ.mɐ] 宝石；蛋黄；芽&lt;名&gt;</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
@@ -13305,7 +13341,7 @@
       </c>
       <c r="D404" s="1" t="inlineStr">
         <is>
-          <t>宝石</t>
+          <t>宝石；蛋黄；芽</t>
         </is>
       </c>
       <c r="E404" s="1" t="inlineStr">
@@ -13396,7 +13432,7 @@
       </c>
       <c r="C407" s="1" t="inlineStr">
         <is>
-          <t>ab.sow.vi.ˈsãʊ̃</t>
+          <t>/ab.sow.vi.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D407" s="1" t="inlineStr">
@@ -13460,7 +13496,7 @@
       </c>
       <c r="C409" s="1" t="inlineStr">
         <is>
-          <t>a.sa.si.ˈna.ɾãʊ̃</t>
+          <t>/a.sa.si.ˈna.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D409" s="1" t="inlineStr">
@@ -14383,7 +14419,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>[maˈsa(ʁ)] 钻孔&lt;动&gt;</t>
+          <t>[maˈsa(ʁ)] 烤焦；烧焦；使厌烦&lt;动&gt;</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
@@ -14393,7 +14429,7 @@
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t>钻孔</t>
+          <t>烤焦；烧焦；使厌烦</t>
         </is>
       </c>
       <c r="E438" s="1" t="inlineStr">
@@ -14479,13 +14515,17 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>直截了当&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C441" s="1" t="inlineStr"/>
+          <t>抵近射击；近距离平射&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C441" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkej.mɐ ˈʁo(w).pɐ/</t>
+        </is>
+      </c>
       <c r="D441" s="1" t="inlineStr">
         <is>
-          <t>直截了当</t>
+          <t>抵近射击；近距离平射</t>
         </is>
       </c>
       <c r="E441" s="1" t="inlineStr">
@@ -14702,7 +14742,11 @@
           <t>编号&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C448" s="1" t="inlineStr"/>
+      <c r="C448" s="1" t="inlineStr">
+        <is>
+          <t>/ˈid/</t>
+        </is>
+      </c>
       <c r="D448" s="1" t="inlineStr">
         <is>
           <t>编号</t>
@@ -14759,7 +14803,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>[de.po.ziˈta(ʁ)] 押金&lt;动&gt;</t>
+          <t>[de.po.ziˈta(ʁ)] 存放；储蓄；寄存&lt;动&gt;</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
@@ -14769,7 +14813,7 @@
       </c>
       <c r="D450" s="1" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>存放；储蓄；寄存</t>
         </is>
       </c>
       <c r="E450" s="1" t="inlineStr">
@@ -14956,7 +15000,7 @@
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t>ʒũ.ˈta.ɾãʊ̃</t>
+          <t>/ʒũ.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D456" s="1" t="inlineStr">
@@ -15178,7 +15222,11 @@
           <t>嗯&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C463" s="1" t="inlineStr"/>
+      <c r="C463" s="1" t="inlineStr">
+        <is>
+          <t>/m/</t>
+        </is>
+      </c>
       <c r="D463" s="1" t="inlineStr">
         <is>
           <t>嗯</t>
@@ -15235,7 +15283,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>[baˈni(ʁ)] 禁令&lt;动&gt;</t>
+          <t>[baˈni(ʁ)] 禁止；放逐；驱逐&lt;动&gt;</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
@@ -15245,7 +15293,7 @@
       </c>
       <c r="D465" s="1" t="inlineStr">
         <is>
-          <t>禁令</t>
+          <t>禁止；放逐；驱逐</t>
         </is>
       </c>
       <c r="E465" s="1" t="inlineStr">
@@ -15526,7 +15574,11 @@
           <t>放射性的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C474" s="1" t="inlineStr"/>
+      <c r="C474" s="1" t="inlineStr">
+        <is>
+          <t>/ʁa.d͡ʒjo.akˈti.vu/</t>
+        </is>
+      </c>
       <c r="D474" s="1" t="inlineStr">
         <is>
           <t>放射性的</t>
@@ -16095,7 +16147,7 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>[aʁ.ma.zeˈna(ʁ)] 商店&lt;动&gt;</t>
+          <t>[aʁ.ma.zeˈna(ʁ)] 储存；贮藏；囤积&lt;动&gt;</t>
         </is>
       </c>
       <c r="C492" s="1" t="inlineStr">
@@ -16105,7 +16157,7 @@
       </c>
       <c r="D492" s="1" t="inlineStr">
         <is>
-          <t>商店</t>
+          <t>储存；贮藏；囤积</t>
         </is>
       </c>
       <c r="E492" s="1" t="inlineStr">
@@ -16228,7 +16280,7 @@
       </c>
       <c r="C496" s="1" t="inlineStr">
         <is>
-          <t>xe.ve.ˈla.ɾãʊ̃</t>
+          <t>/xe.ve.ˈla.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D496" s="1" t="inlineStr">
@@ -16383,7 +16435,7 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>[fowˈɡa(ʁ)] 懈怠&lt;动&gt;</t>
+          <t>[/fowˈɡa(ʁ)/] 高兴&lt;动&gt;；欢庆&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C501" s="1" t="inlineStr">
@@ -16393,7 +16445,7 @@
       </c>
       <c r="D501" s="1" t="inlineStr">
         <is>
-          <t>懈怠</t>
+          <t>高兴&lt;动&gt;；欢庆&lt;动&gt;</t>
         </is>
       </c>
       <c r="E501" s="1" t="inlineStr">
@@ -16415,7 +16467,7 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>[is.peˈka(ʁ)] 等待&lt;动&gt;</t>
+          <t>[/is.peˈka(ʁ)/] 等待；等候&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C502" s="1" t="inlineStr">
@@ -16425,7 +16477,7 @@
       </c>
       <c r="D502" s="1" t="inlineStr">
         <is>
-          <t>等待</t>
+          <t>等待；等候</t>
         </is>
       </c>
       <c r="E502" s="1" t="inlineStr">
@@ -16575,7 +16627,7 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>[tɾɐ̃ˈsa(ʁ)] 辫子&lt;动&gt;</t>
+          <t>[tɾɐ̃ˈsa(ʁ)] 编织；编（辫子）&lt;动&gt;</t>
         </is>
       </c>
       <c r="C507" s="1" t="inlineStr">
@@ -16585,7 +16637,7 @@
       </c>
       <c r="D507" s="1" t="inlineStr">
         <is>
-          <t>辫子</t>
+          <t>编织；编（辫子）</t>
         </is>
       </c>
       <c r="E507" s="1" t="inlineStr">
@@ -16932,7 +16984,7 @@
       </c>
       <c r="C518" s="1" t="inlineStr">
         <is>
-          <t>ˈdʒĩ.nə</t>
+          <t>/ˈdʒĩ.nə/</t>
         </is>
       </c>
       <c r="D518" s="1" t="inlineStr">
@@ -17439,17 +17491,17 @@
       </c>
       <c r="B534" s="1" t="inlineStr">
         <is>
-          <t>[ka.ˈi.dʊs] 堕落&lt;名&gt;</t>
+          <t>[ka.ˈi.dʊs] 倒下的；坠落的；跌倒的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C534" s="1" t="inlineStr">
         <is>
-          <t>ka.ˈi.dʊs</t>
+          <t>/ka.ˈi.dʊs/</t>
         </is>
       </c>
       <c r="D534" s="1" t="inlineStr">
         <is>
-          <t>堕落</t>
+          <t>倒下的；坠落的；跌倒的</t>
         </is>
       </c>
       <c r="E534" s="1" t="inlineStr">
@@ -17599,7 +17651,7 @@
       </c>
       <c r="B539" s="1" t="inlineStr">
         <is>
-          <t>[pĩˈta.dɐ] 画的&lt;名&gt;</t>
+          <t>[/pĩˈta.dɐ/] 珠鸡；珍珠鸡&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C539" s="1" t="inlineStr">
@@ -17609,7 +17661,7 @@
       </c>
       <c r="D539" s="1" t="inlineStr">
         <is>
-          <t>画的</t>
+          <t>珠鸡；珍珠鸡&lt;名&gt;</t>
         </is>
       </c>
       <c r="E539" s="1" t="inlineStr">
@@ -17695,7 +17747,7 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>[miˈlɔʁ.d͡ʒi] 陛下&lt;名&gt;</t>
+          <t>[miˈlɔʁ.d͡ʒi] 大人；老爷；阁下&lt;名&gt;</t>
         </is>
       </c>
       <c r="C542" s="1" t="inlineStr">
@@ -17705,7 +17757,7 @@
       </c>
       <c r="D542" s="1" t="inlineStr">
         <is>
-          <t>陛下</t>
+          <t>大人；老爷；阁下</t>
         </is>
       </c>
       <c r="E542" s="1" t="inlineStr">
@@ -17983,7 +18035,7 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>[ˈna.bu] 萝卜&lt;名&gt;</t>
+          <t>[/ˈna.bu/] 芜菁；萝卜&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C551" s="1" t="inlineStr">
@@ -17993,7 +18045,7 @@
       </c>
       <c r="D551" s="1" t="inlineStr">
         <is>
-          <t>萝卜</t>
+          <t>芜菁；萝卜&lt;名&gt;</t>
         </is>
       </c>
       <c r="E551" s="1" t="inlineStr">
@@ -18079,7 +18131,7 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>[poˈli(ʁ)] 波兰语&lt;动&gt;</t>
+          <t>[poˈli(ʁ)] 抛光；磨光；擦亮&lt;动&gt;</t>
         </is>
       </c>
       <c r="C554" s="1" t="inlineStr">
@@ -18089,7 +18141,7 @@
       </c>
       <c r="D554" s="1" t="inlineStr">
         <is>
-          <t>波兰语</t>
+          <t>抛光；磨光；擦亮</t>
         </is>
       </c>
       <c r="E554" s="1" t="inlineStr">
@@ -18114,7 +18166,11 @@
           <t>紧身衣&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C555" s="1" t="inlineStr"/>
+      <c r="C555" s="1" t="inlineStr">
+        <is>
+          <t>/kɔˈlɐ̃s/</t>
+        </is>
+      </c>
       <c r="D555" s="1" t="inlineStr">
         <is>
           <t>紧身衣</t>
@@ -18363,7 +18419,7 @@
       </c>
       <c r="B563" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɛst͡ʃ] 最好的&lt;名&gt;</t>
+          <t>[ˈbɛst͡ʃ] 愚蠢的；笨的；傻的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C563" s="1" t="inlineStr">
@@ -18373,7 +18429,7 @@
       </c>
       <c r="D563" s="1" t="inlineStr">
         <is>
-          <t>最好的</t>
+          <t>愚蠢的；笨的；傻的</t>
         </is>
       </c>
       <c r="E563" s="1" t="inlineStr">
@@ -18528,7 +18584,7 @@
       </c>
       <c r="C568" s="1" t="inlineStr">
         <is>
-          <t>ˈle.ẽỹ</t>
+          <t>/ˈle.ẽỹ/</t>
         </is>
       </c>
       <c r="D568" s="1" t="inlineStr">
@@ -18779,7 +18835,7 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>[ˈpis.kɐ] 闪烁&lt;名&gt;</t>
+          <t>[/ˈpis.kɐ/] 眨眼；转向灯&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C576" s="1" t="inlineStr">
@@ -18789,7 +18845,7 @@
       </c>
       <c r="D576" s="1" t="inlineStr">
         <is>
-          <t>闪烁</t>
+          <t>眨眼；转向灯&lt;名&gt;</t>
         </is>
       </c>
       <c r="E576" s="1" t="inlineStr">
@@ -18811,7 +18867,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>[ˈsa.fu] 萨福&lt;名&gt;</t>
+          <t>[ˈsa.fu] 机敏的；精明的；消息灵通的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C577" s="1" t="inlineStr">
@@ -18821,7 +18877,7 @@
       </c>
       <c r="D577" s="1" t="inlineStr">
         <is>
-          <t>萨福</t>
+          <t>机敏的；精明的；消息灵通的</t>
         </is>
       </c>
       <c r="E577" s="1" t="inlineStr">
@@ -18875,17 +18931,17 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>[ˈsay.ɾãʊ̃] 左&lt;动&gt;</t>
+          <t>[ˈsay.ɾãʊ̃] 离开；出去&lt;动&gt;</t>
         </is>
       </c>
       <c r="C579" s="1" t="inlineStr">
         <is>
-          <t>ˈsay.ɾãʊ̃</t>
+          <t>/ˈsay.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D579" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>离开；出去</t>
         </is>
       </c>
       <c r="E579" s="1" t="inlineStr">
@@ -19003,7 +19059,7 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>[vo.aˈdo.ɾɐ] 飞行&lt;名&gt;</t>
+          <t>[vo.aˈdo.ɾɐ] 飞行的；飞踢&lt;名&gt;</t>
         </is>
       </c>
       <c r="C583" s="1" t="inlineStr">
@@ -19013,7 +19069,7 @@
       </c>
       <c r="D583" s="1" t="inlineStr">
         <is>
-          <t>飞行</t>
+          <t>飞行的；飞踢</t>
         </is>
       </c>
       <c r="E583" s="1" t="inlineStr">
@@ -19168,7 +19224,7 @@
       </c>
       <c r="C588" s="1" t="inlineStr">
         <is>
-          <t>a.si.o.ˈnis.tə</t>
+          <t>/a.si.o.ˈnis.tə/</t>
         </is>
       </c>
       <c r="D588" s="1" t="inlineStr">
@@ -19227,7 +19283,7 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>[ʃaˈlõ] 沙洛姆&lt;叹&gt;</t>
+          <t>[ʃaˈlõ] 和平；你好；再见&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C590" s="1" t="inlineStr">
@@ -19237,7 +19293,7 @@
       </c>
       <c r="D590" s="1" t="inlineStr">
         <is>
-          <t>沙洛姆</t>
+          <t>和平；你好；再见</t>
         </is>
       </c>
       <c r="E590" s="1" t="inlineStr">
@@ -19483,7 +19539,7 @@
       </c>
       <c r="B598" s="1" t="inlineStr">
         <is>
-          <t>[as.piˈɾa(ʁ)] 真空&lt;动&gt;</t>
+          <t>[as.piˈɾa(ʁ)] 吸入；抽吸；渴望；追求&lt;动&gt;</t>
         </is>
       </c>
       <c r="C598" s="1" t="inlineStr">
@@ -19493,7 +19549,7 @@
       </c>
       <c r="D598" s="1" t="inlineStr">
         <is>
-          <t>真空</t>
+          <t>吸入；抽吸；渴望；追求</t>
         </is>
       </c>
       <c r="E598" s="1" t="inlineStr">
@@ -19904,7 +19960,7 @@
       </c>
       <c r="C611" s="1" t="inlineStr">
         <is>
-          <t>es.kõ.ˈde.ɾãʊ̃</t>
+          <t>/es.kõ.ˈde.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D611" s="1" t="inlineStr">
@@ -20795,7 +20851,7 @@
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
-          <t>[pajˈɾa(ʁ)] 派拉尔&lt;动&gt;</t>
+          <t>[pajˈɾa(ʁ)] 盘旋；翱翔；萦绕&lt;动&gt;</t>
         </is>
       </c>
       <c r="C639" s="1" t="inlineStr">
@@ -20805,7 +20861,7 @@
       </c>
       <c r="D639" s="1" t="inlineStr">
         <is>
-          <t>派拉尔</t>
+          <t>盘旋；翱翔；萦绕</t>
         </is>
       </c>
       <c r="E639" s="1" t="inlineStr">
@@ -21019,7 +21075,7 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>[deˈvɔ.tu] 德沃托&lt;名&gt;</t>
+          <t>[deˈvɔ.tu] 虔诚的；虔诚信徒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C646" s="1" t="inlineStr">
@@ -21029,7 +21085,7 @@
       </c>
       <c r="D646" s="1" t="inlineStr">
         <is>
-          <t>德沃托</t>
+          <t>虔诚的；虔诚信徒</t>
         </is>
       </c>
       <c r="E646" s="1" t="inlineStr">
@@ -21051,7 +21107,7 @@
       </c>
       <c r="B647" s="1" t="inlineStr">
         <is>
-          <t>[ˈd͡ʒi.zew] 柴油机&lt;名&gt;</t>
+          <t>[/ˈd͡ʒi.zew/] 柴油&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C647" s="1" t="inlineStr">
@@ -21061,7 +21117,7 @@
       </c>
       <c r="D647" s="1" t="inlineStr">
         <is>
-          <t>柴油机</t>
+          <t>柴油</t>
         </is>
       </c>
       <c r="E647" s="1" t="inlineStr">
@@ -21152,7 +21208,7 @@
       </c>
       <c r="C650" s="1" t="inlineStr">
         <is>
-          <t>a.si.ˈna.ɾãʊ̃</t>
+          <t>/a.si.ˈna.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D650" s="1" t="inlineStr">
@@ -21211,7 +21267,7 @@
       </c>
       <c r="B652" s="1" t="inlineStr">
         <is>
-          <t>[a.te.ɾaˈdoʁ] 阿特拉多尔&lt;形&gt;</t>
+          <t>[a.te.ɾaˈdoʁ] 可怕的；骇人的；令人恐惧的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C652" s="1" t="inlineStr">
@@ -21221,7 +21277,7 @@
       </c>
       <c r="D652" s="1" t="inlineStr">
         <is>
-          <t>阿特拉多尔</t>
+          <t>可怕的；骇人的；令人恐惧的</t>
         </is>
       </c>
       <c r="E652" s="1" t="inlineStr">
@@ -21243,7 +21299,7 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>[feˈʁu.ʒẽj̃] 铁矿&lt;名&gt;</t>
+          <t>[feˈʁu.ʒẽj̃] 铁锈；锈病&lt;名&gt;</t>
         </is>
       </c>
       <c r="C653" s="1" t="inlineStr">
@@ -21253,7 +21309,7 @@
       </c>
       <c r="D653" s="1" t="inlineStr">
         <is>
-          <t>铁矿</t>
+          <t>铁锈；锈病</t>
         </is>
       </c>
       <c r="E653" s="1" t="inlineStr">
@@ -21339,7 +21395,7 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>[flo.ɾeˈse(ʁ)] 弗洛雷斯&lt;动&gt;</t>
+          <t>[flo.ɾeˈse(ʁ)] 开花；繁荣；兴旺&lt;动&gt;</t>
         </is>
       </c>
       <c r="C656" s="1" t="inlineStr">
@@ -21349,7 +21405,7 @@
       </c>
       <c r="D656" s="1" t="inlineStr">
         <is>
-          <t>弗洛雷斯</t>
+          <t>开花；繁荣；兴旺</t>
         </is>
       </c>
       <c r="E656" s="1" t="inlineStr">
@@ -21467,7 +21523,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>[de.zẽˈbaʁ.ki] 德森巴克&lt;名&gt;</t>
+          <t>[de.zẽˈbaʁ.ki] 下船；下机；登陆；卸货&lt;名&gt;</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
@@ -21477,7 +21533,7 @@
       </c>
       <c r="D660" s="1" t="inlineStr">
         <is>
-          <t>德森巴克</t>
+          <t>下船；下机；登陆；卸货</t>
         </is>
       </c>
       <c r="E660" s="1" t="inlineStr">
@@ -21499,7 +21555,7 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.te.d͡ʒiˈa.du] 恩泰迪亚多&lt;形&gt;</t>
+          <t>[ẽ.te.d͡ʒiˈa.du] 无聊的；厌倦的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C661" s="1" t="inlineStr">
@@ -21509,7 +21565,7 @@
       </c>
       <c r="D661" s="1" t="inlineStr">
         <is>
-          <t>恩泰迪亚多</t>
+          <t>无聊的；厌倦的</t>
         </is>
       </c>
       <c r="E661" s="1" t="inlineStr">
@@ -21563,7 +21619,7 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>[viˈʒi.ljɐ] 维吉利亚&lt;名&gt;</t>
+          <t>[viˈʒi.ljɐ] 守夜；不眠之夜；节日前夜&lt;名&gt;</t>
         </is>
       </c>
       <c r="C663" s="1" t="inlineStr">
@@ -21573,7 +21629,7 @@
       </c>
       <c r="D663" s="1" t="inlineStr">
         <is>
-          <t>维吉利亚</t>
+          <t>守夜；不眠之夜；节日前夜</t>
         </is>
       </c>
       <c r="E663" s="1" t="inlineStr">
@@ -21627,7 +21683,7 @@
       </c>
       <c r="B665" s="1" t="inlineStr">
         <is>
-          <t>[ʁisˈka(ʁ)] 里斯卡&lt;动&gt;</t>
+          <t>[ʁisˈka(ʁ)] 划线；划掉；取消；擦伤&lt;动&gt;</t>
         </is>
       </c>
       <c r="C665" s="1" t="inlineStr">
@@ -21637,7 +21693,7 @@
       </c>
       <c r="D665" s="1" t="inlineStr">
         <is>
-          <t>里斯卡</t>
+          <t>划线；划掉；取消；擦伤</t>
         </is>
       </c>
       <c r="E665" s="1" t="inlineStr">
@@ -21691,7 +21747,7 @@
       </c>
       <c r="B667" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾa.du] 普拉多&lt;名&gt;</t>
+          <t>[ˈpɾa.du] 草地；牧场&lt;名&gt;</t>
         </is>
       </c>
       <c r="C667" s="1" t="inlineStr">
@@ -21701,7 +21757,7 @@
       </c>
       <c r="D667" s="1" t="inlineStr">
         <is>
-          <t>普拉多</t>
+          <t>草地；牧场</t>
         </is>
       </c>
       <c r="E667" s="1" t="inlineStr">
@@ -21723,7 +21779,7 @@
       </c>
       <c r="B668" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.ves.t͡ʃiˈmẽ.tu] 重演&lt;名&gt;</t>
+          <t>[ʁe.ves.t͡ʃiˈmẽ.tu] 覆盖层；涂层；衬里&lt;名&gt;</t>
         </is>
       </c>
       <c r="C668" s="1" t="inlineStr">
@@ -21733,7 +21789,7 @@
       </c>
       <c r="D668" s="1" t="inlineStr">
         <is>
-          <t>重演</t>
+          <t>覆盖层；涂层；衬里</t>
         </is>
       </c>
       <c r="E668" s="1" t="inlineStr">
@@ -21755,7 +21811,7 @@
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>[e.vaˈzɐ̃w̃] 埃瓦桑&lt;名&gt;</t>
+          <t>[e.vaˈzɐ̃w̃] 逃避；逃脱；辍学；流失&lt;名&gt;</t>
         </is>
       </c>
       <c r="C669" s="1" t="inlineStr">
@@ -21765,7 +21821,7 @@
       </c>
       <c r="D669" s="1" t="inlineStr">
         <is>
-          <t>埃瓦桑</t>
+          <t>逃避；逃脱；辍学；流失</t>
         </is>
       </c>
       <c r="E669" s="1" t="inlineStr">
@@ -21787,7 +21843,7 @@
       </c>
       <c r="B670" s="1" t="inlineStr">
         <is>
-          <t>[mu.ʎeˈɾẽ.ɡu] 穆莱伦戈&lt;名&gt;</t>
+          <t>[mu.ʎeˈɾẽ.ɡu] 好色之徒；玩弄女性者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C670" s="1" t="inlineStr">
@@ -21797,7 +21853,7 @@
       </c>
       <c r="D670" s="1" t="inlineStr">
         <is>
-          <t>穆莱伦戈</t>
+          <t>好色之徒；玩弄女性者</t>
         </is>
       </c>
       <c r="E670" s="1" t="inlineStr">
@@ -21856,7 +21912,7 @@
       </c>
       <c r="C672" s="1" t="inlineStr">
         <is>
-          <t>doɣ.ˈmi.ɾãʊ̃</t>
+          <t>/doɣ.ˈmi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D672" s="1" t="inlineStr">
@@ -21915,13 +21971,17 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>不。&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C674" s="1" t="inlineStr"/>
+          <t>号码；编号&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C674" s="1" t="inlineStr">
+        <is>
+          <t>/ˈnũ.me.ɾu/</t>
+        </is>
+      </c>
       <c r="D674" s="1" t="inlineStr">
         <is>
-          <t>不。</t>
+          <t>号码；编号</t>
         </is>
       </c>
       <c r="E674" s="1" t="inlineStr">
@@ -21975,7 +22035,7 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>[pɾo.iˈbi(ʁ)] 普罗伊比尔&lt;动&gt;</t>
+          <t>[pɾo.iˈbi(ʁ)] 禁止；不许&lt;动&gt;</t>
         </is>
       </c>
       <c r="C676" s="1" t="inlineStr">
@@ -21985,7 +22045,7 @@
       </c>
       <c r="D676" s="1" t="inlineStr">
         <is>
-          <t>普罗伊比尔</t>
+          <t>禁止；不许</t>
         </is>
       </c>
       <c r="E676" s="1" t="inlineStr">
@@ -22199,7 +22259,7 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>[tɾɐ̃s.plɐ̃ˈta(ʁ)] 移植物&lt;动&gt;</t>
+          <t>[tɾɐ̃s.plɐ̃ˈta(ʁ)] 移植；移栽&lt;动&gt;</t>
         </is>
       </c>
       <c r="C683" s="1" t="inlineStr">
@@ -22209,7 +22269,7 @@
       </c>
       <c r="D683" s="1" t="inlineStr">
         <is>
-          <t>移植物</t>
+          <t>移植；移栽</t>
         </is>
       </c>
       <c r="E683" s="1" t="inlineStr">
@@ -22231,7 +22291,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>[ɡu.loˈzej.mɐ] 对待&lt;名&gt;</t>
+          <t>[ɡu.loˈzej.mɐ] 甜食；糖果；零食&lt;名&gt;</t>
         </is>
       </c>
       <c r="C684" s="1" t="inlineStr">
@@ -22241,7 +22301,7 @@
       </c>
       <c r="D684" s="1" t="inlineStr">
         <is>
-          <t>对待</t>
+          <t>甜食；糖果；零食</t>
         </is>
       </c>
       <c r="E684" s="1" t="inlineStr">
@@ -22263,7 +22323,7 @@
       </c>
       <c r="B685" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁi.ʃɐ] 里克萨&lt;名&gt;</t>
+          <t>[ˈʁi.ʃɐ] 争吵；宿怨&lt;名&gt;</t>
         </is>
       </c>
       <c r="C685" s="1" t="inlineStr">
@@ -22273,7 +22333,7 @@
       </c>
       <c r="D685" s="1" t="inlineStr">
         <is>
-          <t>里克萨</t>
+          <t>争吵；宿怨</t>
         </is>
       </c>
       <c r="E685" s="1" t="inlineStr">
@@ -22396,7 +22456,7 @@
       </c>
       <c r="C689" s="1" t="inlineStr">
         <is>
-          <t>a.dʒi.a.ˈmẽ.tʊ</t>
+          <t>/a.dʒi.a.ˈmẽ.tʊ/</t>
         </is>
       </c>
       <c r="D689" s="1" t="inlineStr">
@@ -22711,7 +22771,7 @@
       </c>
       <c r="B699" s="1" t="inlineStr">
         <is>
-          <t>[kuˈʎɐ̃w̃] 球&lt;名&gt;</t>
+          <t>[kuˈʎɐ̃w̃] 睾丸&lt;名&gt;</t>
         </is>
       </c>
       <c r="C699" s="1" t="inlineStr">
@@ -22721,7 +22781,7 @@
       </c>
       <c r="D699" s="1" t="inlineStr">
         <is>
-          <t>球</t>
+          <t>睾丸</t>
         </is>
       </c>
       <c r="E699" s="1" t="inlineStr">
@@ -22903,7 +22963,7 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃĩ.nu] 奇诺&lt;名&gt;</t>
+          <t>[/ˈʃĩ.nu/] 发卷；卷发&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C705" s="1" t="inlineStr">
@@ -22913,7 +22973,7 @@
       </c>
       <c r="D705" s="1" t="inlineStr">
         <is>
-          <t>奇诺</t>
+          <t>发卷；卷发&lt;名&gt;</t>
         </is>
       </c>
       <c r="E705" s="1" t="inlineStr">
@@ -22938,7 +22998,11 @@
           <t>他妈的&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C706" s="1" t="inlineStr"/>
+      <c r="C706" s="1" t="inlineStr">
+        <is>
+          <t>/fodˈasse/</t>
+        </is>
+      </c>
       <c r="D706" s="1" t="inlineStr">
         <is>
           <t>他妈的</t>
@@ -22995,7 +23059,7 @@
       </c>
       <c r="B708" s="1" t="inlineStr">
         <is>
-          <t>[aˈdɛp.tu] 熟练的&lt;名&gt;</t>
+          <t>[aˈdɛp.tu] 信徒；拥护者；爱好者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C708" s="1" t="inlineStr">
@@ -23005,7 +23069,7 @@
       </c>
       <c r="D708" s="1" t="inlineStr">
         <is>
-          <t>熟练的</t>
+          <t>信徒；拥护者；爱好者</t>
         </is>
       </c>
       <c r="E708" s="1" t="inlineStr">
@@ -23062,10 +23126,14 @@
           <t>棉&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C710" s="1" t="inlineStr"/>
+      <c r="C710" s="1" t="inlineStr">
+        <is>
+          <t>/kˈotton/</t>
+        </is>
+      </c>
       <c r="D710" s="1" t="inlineStr">
         <is>
-          <t>棉</t>
+          <t>（英语词）棉；葡语应为 algodão</t>
         </is>
       </c>
       <c r="E710" s="1" t="inlineStr">
@@ -23087,13 +23155,17 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>拖车&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C711" s="1" t="inlineStr"/>
+          <t>[[ʁuˈlɔ.tɨ]] 大篷车，活动住房&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C711" s="1" t="inlineStr">
+        <is>
+          <t>/ʁoulˈotte/</t>
+        </is>
+      </c>
       <c r="D711" s="1" t="inlineStr">
         <is>
-          <t>拖车</t>
+          <t>大篷车，活动住房</t>
         </is>
       </c>
       <c r="E711" s="1" t="inlineStr">
@@ -23152,7 +23224,7 @@
       </c>
       <c r="C713" s="1" t="inlineStr">
         <is>
-          <t>ˈta.tʃi.kʊ</t>
+          <t>/ˈta.tʃi.kʊ/</t>
         </is>
       </c>
       <c r="D713" s="1" t="inlineStr">
@@ -23179,7 +23251,7 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>[tɾɐ̃ˈza(ʁ)] 他妈的&lt;动&gt;</t>
+          <t>[tɾɐ̃ˈza(ʁ)] 性交；交易；达成协议&lt;动&gt;</t>
         </is>
       </c>
       <c r="C714" s="1" t="inlineStr">
@@ -23189,7 +23261,7 @@
       </c>
       <c r="D714" s="1" t="inlineStr">
         <is>
-          <t>他妈的</t>
+          <t>性交；交易；达成协议</t>
         </is>
       </c>
       <c r="E714" s="1" t="inlineStr">
@@ -23307,7 +23379,7 @@
       </c>
       <c r="B718" s="1" t="inlineStr">
         <is>
-          <t>[se.ɾiˈa(ʁ)] 连续剧&lt;动&gt;</t>
+          <t>[se.ɾiˈa(ʁ)] 排成系列；连载&lt;动&gt;</t>
         </is>
       </c>
       <c r="C718" s="1" t="inlineStr">
@@ -23317,7 +23389,7 @@
       </c>
       <c r="D718" s="1" t="inlineStr">
         <is>
-          <t>连续剧</t>
+          <t>排成系列；连载</t>
         </is>
       </c>
       <c r="E718" s="1" t="inlineStr">
@@ -23568,7 +23640,7 @@
       </c>
       <c r="C726" s="1" t="inlineStr">
         <is>
-          <t>kõ.tɾa.ˈsãʊ̃</t>
+          <t>/kõ.tɾa.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D726" s="1" t="inlineStr">
@@ -23659,7 +23731,7 @@
       </c>
       <c r="B729" s="1" t="inlineStr">
         <is>
-          <t>[is.koˈʁɛ.ɡɐ] 滑倒&lt;名&gt;</t>
+          <t>[/is.koˈʁɛ.ɡɐ/] 滑动；滑道&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C729" s="1" t="inlineStr">
@@ -23669,7 +23741,7 @@
       </c>
       <c r="D729" s="1" t="inlineStr">
         <is>
-          <t>滑倒</t>
+          <t>滑动；滑道&lt;名&gt;</t>
         </is>
       </c>
       <c r="E729" s="1" t="inlineStr">
@@ -23691,7 +23763,7 @@
       </c>
       <c r="B730" s="1" t="inlineStr">
         <is>
-          <t>[kõ.t͡ʃi.nẽˈtaw] 欧陆式&lt;名&gt;</t>
+          <t>[/kõ.t͡ʃi.nẽˈtaw/] 欧陆式的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C730" s="1" t="inlineStr">
@@ -23701,7 +23773,7 @@
       </c>
       <c r="D730" s="1" t="inlineStr">
         <is>
-          <t>欧陆式</t>
+          <t>欧陆式的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E730" s="1" t="inlineStr">
@@ -23819,7 +23891,7 @@
       </c>
       <c r="B734" s="1" t="inlineStr">
         <is>
-          <t>[isˈfɾɛ.ɡɐ] 磨砂膏&lt;名&gt;</t>
+          <t>[/isˈfɾɛ.ɡɐ/] 擦；摩擦&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C734" s="1" t="inlineStr">
@@ -23829,7 +23901,7 @@
       </c>
       <c r="D734" s="1" t="inlineStr">
         <is>
-          <t>磨砂膏</t>
+          <t>擦；摩擦&lt;名&gt;</t>
         </is>
       </c>
       <c r="E734" s="1" t="inlineStr">
@@ -23888,7 +23960,7 @@
       </c>
       <c r="C736" s="1" t="inlineStr">
         <is>
-          <t>a.me.a.ˈsa.ɾãʊ̃</t>
+          <t>/a.me.a.ˈsa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D736" s="1" t="inlineStr">
@@ -23947,7 +24019,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>[ˈmɛ.ɡɐ] 巨型&lt;名&gt;</t>
+          <t>[/ˈmɛ.ɡɐ/] 兆；巨大的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
@@ -23957,7 +24029,7 @@
       </c>
       <c r="D738" s="1" t="inlineStr">
         <is>
-          <t>巨型</t>
+          <t>兆；巨大的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E738" s="1" t="inlineStr">
@@ -23979,7 +24051,7 @@
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃiw] 邱&lt;叹&gt;</t>
+          <t>[ˈʃiw] 嘘&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C739" s="1" t="inlineStr">
@@ -23989,7 +24061,7 @@
       </c>
       <c r="D739" s="1" t="inlineStr">
         <is>
-          <t>邱</t>
+          <t>嘘</t>
         </is>
       </c>
       <c r="E739" s="1" t="inlineStr">
@@ -24400,7 +24472,7 @@
       </c>
       <c r="C752" s="1" t="inlineStr">
         <is>
-          <t>ˈa.lẽỹ</t>
+          <t>/ˈa.lẽỹ/</t>
         </is>
       </c>
       <c r="D752" s="1" t="inlineStr">
@@ -24747,7 +24819,7 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>[ko.moˈvi.du] 搬家了&lt;形&gt;</t>
+          <t>[ko.moˈvi.du] 感动的；动容的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C763" s="1" t="inlineStr">
@@ -24757,7 +24829,7 @@
       </c>
       <c r="D763" s="1" t="inlineStr">
         <is>
-          <t>搬家了</t>
+          <t>感动的；动容的</t>
         </is>
       </c>
       <c r="E763" s="1" t="inlineStr">
@@ -24880,7 +24952,7 @@
       </c>
       <c r="C767" s="1" t="inlineStr">
         <is>
-          <t>a.kõ.pã.ɲa.ˈmẽ.tʊ</t>
+          <t>/a.kõ.pã.ɲa.ˈmẽ.tʊ/</t>
         </is>
       </c>
       <c r="D767" s="1" t="inlineStr">
@@ -24939,7 +25011,7 @@
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.seˈna(ʁ)] 舞台&lt;动&gt;</t>
+          <t>[ẽ.seˈna(ʁ)] 上演；把…搬上舞台&lt;动&gt;</t>
         </is>
       </c>
       <c r="C769" s="1" t="inlineStr">
@@ -24949,7 +25021,7 @@
       </c>
       <c r="D769" s="1" t="inlineStr">
         <is>
-          <t>舞台</t>
+          <t>上演；把…搬上舞台</t>
         </is>
       </c>
       <c r="E769" s="1" t="inlineStr">
@@ -25035,17 +25107,17 @@
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>[u.ˈsi] 乌西&lt;名&gt;</t>
+          <t>[u.ˈsi] 重症监护室&lt;名&gt;</t>
         </is>
       </c>
       <c r="C772" s="1" t="inlineStr">
         <is>
-          <t>u.ˈsi</t>
+          <t>/u.ˈsi/</t>
         </is>
       </c>
       <c r="D772" s="1" t="inlineStr">
         <is>
-          <t>乌西</t>
+          <t>重症监护室</t>
         </is>
       </c>
       <c r="E772" s="1" t="inlineStr">
@@ -25195,17 +25267,17 @@
       </c>
       <c r="B777" s="1" t="inlineStr">
         <is>
-          <t>[pɾo.ʒe.ˈtax] 项目&lt;动&gt;</t>
+          <t>[pɾo.ʒe.ˈtax] 设计；投射；规划；放映&lt;动&gt;</t>
         </is>
       </c>
       <c r="C777" s="1" t="inlineStr">
         <is>
-          <t>pɾo.ʒe.ˈtax</t>
+          <t>/pɾo.ʒe.ˈtax/</t>
         </is>
       </c>
       <c r="D777" s="1" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>设计；投射；规划；放映</t>
         </is>
       </c>
       <c r="E777" s="1" t="inlineStr">
@@ -25712,7 +25784,7 @@
       </c>
       <c r="C793" s="1" t="inlineStr">
         <is>
-          <t>de.ˈse.ɾãʊ̃</t>
+          <t>/de.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D793" s="1" t="inlineStr">
@@ -25838,7 +25910,11 @@
           <t>与&lt;介&gt;</t>
         </is>
       </c>
-      <c r="C797" s="1" t="inlineStr"/>
+      <c r="C797" s="1" t="inlineStr">
+        <is>
+          <t>/ˈvɛʁ.sus/</t>
+        </is>
+      </c>
       <c r="D797" s="1" t="inlineStr">
         <is>
           <t>与</t>
@@ -25895,7 +25971,7 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>[ʒaˈze(ʁ)] 谎言&lt;动&gt;</t>
+          <t>[ʒaˈze(ʁ)] 躺卧；位于；长眠&lt;动&gt;</t>
         </is>
       </c>
       <c r="C799" s="1" t="inlineStr">
@@ -25905,7 +25981,7 @@
       </c>
       <c r="D799" s="1" t="inlineStr">
         <is>
-          <t>谎言</t>
+          <t>躺卧；位于；长眠</t>
         </is>
       </c>
       <c r="E799" s="1" t="inlineStr">
@@ -25996,7 +26072,7 @@
       </c>
       <c r="C802" s="1" t="inlineStr">
         <is>
-          <t>bap.ˈtʃiz.mʊ</t>
+          <t>/bap.ˈtʃiz.mʊ/</t>
         </is>
       </c>
       <c r="D802" s="1" t="inlineStr">
@@ -26028,7 +26104,7 @@
       </c>
       <c r="C803" s="1" t="inlineStr">
         <is>
-          <t>tɾãs.foɣ.ˈma.ɾãʊ̃</t>
+          <t>/tɾãs.foɣ.ˈma.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D803" s="1" t="inlineStr">
@@ -26087,7 +26163,7 @@
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>[ˈvĩ.ku.lu] 债券&lt;名&gt;</t>
+          <t>[ˈvĩ.ku.lu] 纽带；联系；关系&lt;名&gt;</t>
         </is>
       </c>
       <c r="C805" s="1" t="inlineStr">
@@ -26097,7 +26173,7 @@
       </c>
       <c r="D805" s="1" t="inlineStr">
         <is>
-          <t>债券</t>
+          <t>纽带；联系；关系</t>
         </is>
       </c>
       <c r="E805" s="1" t="inlineStr">
@@ -26188,7 +26264,7 @@
       </c>
       <c r="C808" s="1" t="inlineStr">
         <is>
-          <t>vẽ.ˈse.ɾãʊ̃</t>
+          <t>/vẽ.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D808" s="1" t="inlineStr">
@@ -26503,7 +26579,7 @@
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>[peˈɾaw.tɐ] 佩拉尔塔&lt;名&gt;</t>
+          <t>[peˈɾaw.tɐ] 懒人；贪睡的人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C818" s="1" t="inlineStr">
@@ -26513,7 +26589,7 @@
       </c>
       <c r="D818" s="1" t="inlineStr">
         <is>
-          <t>佩拉尔塔</t>
+          <t>懒人；贪睡的人</t>
         </is>
       </c>
       <c r="E818" s="1" t="inlineStr">
@@ -26698,7 +26774,11 @@
           <t>收养的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C824" s="1" t="inlineStr"/>
+      <c r="C824" s="1" t="inlineStr">
+        <is>
+          <t>/a.dɔpˈt͡ʃi.vu/</t>
+        </is>
+      </c>
       <c r="D824" s="1" t="inlineStr">
         <is>
           <t>收养的</t>
@@ -26760,7 +26840,7 @@
       </c>
       <c r="C826" s="1" t="inlineStr">
         <is>
-          <t>a.do.ˈɾa.ɾãʊ̃</t>
+          <t>/a.do.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D826" s="1" t="inlineStr">
@@ -26790,7 +26870,11 @@
           <t>公鸡&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C827" s="1" t="inlineStr"/>
+      <c r="C827" s="1" t="inlineStr">
+        <is>
+          <t>/ˈga.lu/</t>
+        </is>
+      </c>
       <c r="D827" s="1" t="inlineStr">
         <is>
           <t>公鸡</t>
@@ -26815,7 +26899,7 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>[is.koˈva(ʁ)] 刷子&lt;动&gt;</t>
+          <t>[is.koˈva(ʁ)] 刷；刷洗&lt;动&gt;</t>
         </is>
       </c>
       <c r="C828" s="1" t="inlineStr">
@@ -26825,7 +26909,7 @@
       </c>
       <c r="D828" s="1" t="inlineStr">
         <is>
-          <t>刷子</t>
+          <t>刷；刷洗</t>
         </is>
       </c>
       <c r="E828" s="1" t="inlineStr">
@@ -26943,7 +27027,7 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɛ.klɐ] 钥匙&lt;名&gt;</t>
+          <t>[ˈtɛ.klɐ] 按键；琴键&lt;名&gt;</t>
         </is>
       </c>
       <c r="C832" s="1" t="inlineStr">
@@ -26953,7 +27037,7 @@
       </c>
       <c r="D832" s="1" t="inlineStr">
         <is>
-          <t>钥匙</t>
+          <t>按键；琴键</t>
         </is>
       </c>
       <c r="E832" s="1" t="inlineStr">
@@ -28031,13 +28115,17 @@
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
-          <t>阿约&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C866" s="1" t="inlineStr"/>
+          <t>[[ˈa.ju]] （旧时）家庭教师；侍从&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C866" s="1" t="inlineStr">
+        <is>
+          <t>/ˈa.ju/</t>
+        </is>
+      </c>
       <c r="D866" s="1" t="inlineStr">
         <is>
-          <t>阿约</t>
+          <t>（旧时）家庭教师；侍从&lt;名&gt;</t>
         </is>
       </c>
       <c r="E866" s="1" t="inlineStr">
@@ -28059,7 +28147,7 @@
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃi.ki] 勾选&lt;名&gt;</t>
+          <t>[/ˈt͡ʃi.ki/] 抽搐；习惯性动作；（勾选）记号&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C867" s="1" t="inlineStr">
@@ -28069,7 +28157,7 @@
       </c>
       <c r="D867" s="1" t="inlineStr">
         <is>
-          <t>勾选</t>
+          <t>抽搐；习惯性动作；（勾选）记号&lt;名&gt;</t>
         </is>
       </c>
       <c r="E867" s="1" t="inlineStr">
@@ -28160,7 +28248,7 @@
       </c>
       <c r="C870" s="1" t="inlineStr">
         <is>
-          <t>ĩ.ko.ˈxɛ.tʊ</t>
+          <t>/ĩ.ko.ˈxɛ.tʊ/</t>
         </is>
       </c>
       <c r="D870" s="1" t="inlineStr">
@@ -28288,7 +28376,7 @@
       </c>
       <c r="C874" s="1" t="inlineStr">
         <is>
-          <t>bap.tʃi.ˈza.dʊ</t>
+          <t>/bap.tʃi.ˈza.dʊ/</t>
         </is>
       </c>
       <c r="D874" s="1" t="inlineStr">
@@ -28446,7 +28534,11 @@
           <t>检查员&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C879" s="1" t="inlineStr"/>
+      <c r="C879" s="1" t="inlineStr">
+        <is>
+          <t>/ĩʃ.pɛkˈto.ɾɐ/</t>
+        </is>
+      </c>
       <c r="D879" s="1" t="inlineStr">
         <is>
           <t>检查员</t>
@@ -28631,7 +28723,7 @@
       </c>
       <c r="B885" s="1" t="inlineStr">
         <is>
-          <t>[soʁˈtej.u] 画&lt;名&gt;</t>
+          <t>[soʁˈtej.u] 抽签；抽奖&lt;名&gt;</t>
         </is>
       </c>
       <c r="C885" s="1" t="inlineStr">
@@ -28641,7 +28733,7 @@
       </c>
       <c r="D885" s="1" t="inlineStr">
         <is>
-          <t>画</t>
+          <t>抽签；抽奖</t>
         </is>
       </c>
       <c r="E885" s="1" t="inlineStr">
@@ -28951,7 +29043,7 @@
       </c>
       <c r="B895" s="1" t="inlineStr">
         <is>
-          <t>[fũˈda(ʁ)] 发现&lt;动&gt;</t>
+          <t>[fũˈda(ʁ)] 创立；建立&lt;动&gt;</t>
         </is>
       </c>
       <c r="C895" s="1" t="inlineStr">
@@ -28961,7 +29053,7 @@
       </c>
       <c r="D895" s="1" t="inlineStr">
         <is>
-          <t>发现</t>
+          <t>创立；建立</t>
         </is>
       </c>
       <c r="E895" s="1" t="inlineStr">
@@ -28983,17 +29075,17 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>[pla.ni.ˈa.ɾãʊ̃] 计划中的&lt;动&gt;</t>
+          <t>[pla.ni.ˈa.ɾãʊ̃] 计划；规划&lt;动&gt;</t>
         </is>
       </c>
       <c r="C896" s="1" t="inlineStr">
         <is>
-          <t>pla.ni.ˈa.ɾãʊ̃</t>
+          <t>/pla.ni.ˈa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D896" s="1" t="inlineStr">
         <is>
-          <t>计划中的</t>
+          <t>计划；规划</t>
         </is>
       </c>
       <c r="E896" s="1" t="inlineStr">
@@ -29116,7 +29208,7 @@
       </c>
       <c r="C900" s="1" t="inlineStr">
         <is>
-          <t>kã.se.ˈla.ɾãʊ̃</t>
+          <t>/kã.se.ˈla.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D900" s="1" t="inlineStr">
@@ -29303,7 +29395,7 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>[kleˈmẽ.t͡ʃi] 克莱门特&lt;形&gt;</t>
+          <t>[kleˈmẽ.t͡ʃi] 仁慈的；宽厚的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C906" s="1" t="inlineStr">
@@ -29313,7 +29405,7 @@
       </c>
       <c r="D906" s="1" t="inlineStr">
         <is>
-          <t>克莱门特</t>
+          <t>仁慈的；宽厚的</t>
         </is>
       </c>
       <c r="E906" s="1" t="inlineStr">
@@ -29399,7 +29491,7 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>[ko.d͡ʒi.fiˈka(ʁ)] 代码&lt;动&gt;</t>
+          <t>[ko.d͡ʒi.fiˈka(ʁ)] 编码；编纂&lt;动&gt;</t>
         </is>
       </c>
       <c r="C909" s="1" t="inlineStr">
@@ -29409,7 +29501,7 @@
       </c>
       <c r="D909" s="1" t="inlineStr">
         <is>
-          <t>代码</t>
+          <t>编码；编纂</t>
         </is>
       </c>
       <c r="E909" s="1" t="inlineStr">
@@ -29564,7 +29656,7 @@
       </c>
       <c r="C914" s="1" t="inlineStr">
         <is>
-          <t>ˈtɪ.ə</t>
+          <t>/ˈtɪ.ə/</t>
         </is>
       </c>
       <c r="D914" s="1" t="inlineStr">
@@ -29722,7 +29814,11 @@
           <t>粉红色&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C919" s="1" t="inlineStr"/>
+      <c r="C919" s="1" t="inlineStr">
+        <is>
+          <t>/ˈpĩ.ki/</t>
+        </is>
+      </c>
       <c r="D919" s="1" t="inlineStr">
         <is>
           <t>粉红色</t>
@@ -29907,7 +30003,7 @@
       </c>
       <c r="B925" s="1" t="inlineStr">
         <is>
-          <t>[ˈmej.ki] 化妆&lt;名&gt;</t>
+          <t>[/ˈmej.ki/] 化妆应为 maquiagem；make 非标准葡语词&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C925" s="1" t="inlineStr">
@@ -29917,7 +30013,7 @@
       </c>
       <c r="D925" s="1" t="inlineStr">
         <is>
-          <t>化妆</t>
+          <t>化妆应为 maquiagem；make 非标准葡语词</t>
         </is>
       </c>
       <c r="E925" s="1" t="inlineStr">
@@ -30136,7 +30232,7 @@
       </c>
       <c r="C932" s="1" t="inlineStr">
         <is>
-          <t>es.plo.ˈdʒi.ɾãʊ̃</t>
+          <t>/es.plo.ˈdʒi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D932" s="1" t="inlineStr">
@@ -30904,7 +31000,7 @@
       </c>
       <c r="C956" s="1" t="inlineStr">
         <is>
-          <t>pi.ˈta.də</t>
+          <t>/pi.ˈta.də/</t>
         </is>
       </c>
       <c r="D956" s="1" t="inlineStr">
@@ -31571,13 +31667,17 @@
       </c>
       <c r="B977" s="1" t="inlineStr">
         <is>
-          <t>被称为&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C977" s="1" t="inlineStr"/>
+          <t>打电话；致电&lt;动&gt;</t>
+        </is>
+      </c>
+      <c r="C977" s="1" t="inlineStr">
+        <is>
+          <t>/te.le.foˈna.ɾɐ̃w̃/</t>
+        </is>
+      </c>
       <c r="D977" s="1" t="inlineStr">
         <is>
-          <t>被称为</t>
+          <t>打电话；致电</t>
         </is>
       </c>
       <c r="E977" s="1" t="inlineStr">
@@ -31764,7 +31864,7 @@
       </c>
       <c r="C983" s="1" t="inlineStr">
         <is>
-          <t>tɾa.ˈʒɛ.tʊ</t>
+          <t>/tɾa.ˈʒɛ.tʊ/</t>
         </is>
       </c>
       <c r="D983" s="1" t="inlineStr">
@@ -32015,7 +32115,7 @@
       </c>
       <c r="B991" s="1" t="inlineStr">
         <is>
-          <t>[do.ku.mẽˈta(ʁ)] 文件&lt;动&gt;</t>
+          <t>[do.ku.mẽˈta(ʁ)] 记录；提供文件证明&lt;动&gt;</t>
         </is>
       </c>
       <c r="C991" s="1" t="inlineStr">
@@ -32025,7 +32125,7 @@
       </c>
       <c r="D991" s="1" t="inlineStr">
         <is>
-          <t>文件</t>
+          <t>记录；提供文件证明</t>
         </is>
       </c>
       <c r="E991" s="1" t="inlineStr">
@@ -32143,7 +32243,7 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>[dɾeˈna(ʁ)] 排水管&lt;动&gt;</t>
+          <t>[dɾeˈna(ʁ)] 排水；引流&lt;动&gt;</t>
         </is>
       </c>
       <c r="C995" s="1" t="inlineStr">
@@ -32153,7 +32253,7 @@
       </c>
       <c r="D995" s="1" t="inlineStr">
         <is>
-          <t>排水管</t>
+          <t>排水；引流</t>
         </is>
       </c>
       <c r="E995" s="1" t="inlineStr">
@@ -32276,7 +32376,7 @@
       </c>
       <c r="C999" s="1" t="inlineStr">
         <is>
-          <t>vo.ˈta.ɾãʊ̃</t>
+          <t>/vo.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D999" s="1" t="inlineStr">
@@ -32434,7 +32534,11 @@
           <t>劳工&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1004" s="1" t="inlineStr"/>
+      <c r="C1004" s="1" t="inlineStr">
+        <is>
+          <t>/mɐ̃w̃ d͡ʒi ˈɔ.bɾɐ/</t>
+        </is>
+      </c>
       <c r="D1004" s="1" t="inlineStr">
         <is>
           <t>劳工</t>
@@ -33291,7 +33395,7 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>[is.koˈʁe(ʁ)] 流量&lt;动&gt;</t>
+          <t>[is.koˈʁe(ʁ)] 流淌；滴落&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1031" s="1" t="inlineStr">
@@ -33301,7 +33405,7 @@
       </c>
       <c r="D1031" s="1" t="inlineStr">
         <is>
-          <t>流量</t>
+          <t>流淌；滴落</t>
         </is>
       </c>
       <c r="E1031" s="1" t="inlineStr">
@@ -33454,7 +33558,11 @@
           <t>说唱歌手&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1036" s="1" t="inlineStr"/>
+      <c r="C1036" s="1" t="inlineStr">
+        <is>
+          <t>/ˈʁɛ.pɐr/</t>
+        </is>
+      </c>
       <c r="D1036" s="1" t="inlineStr">
         <is>
           <t>说唱歌手</t>
@@ -33484,7 +33592,7 @@
       </c>
       <c r="C1037" s="1" t="inlineStr">
         <is>
-          <t>e.ziʃ.ˈtʃi.ɾãʊ̃</t>
+          <t>/e.ziʃ.ˈtʃi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1037" s="1" t="inlineStr">
@@ -33740,7 +33848,7 @@
       </c>
       <c r="C1045" s="1" t="inlineStr">
         <is>
-          <t>ˈpe.ɾəs</t>
+          <t>/ˈpe.ɾəs/</t>
         </is>
       </c>
       <c r="D1045" s="1" t="inlineStr">
@@ -34252,7 +34360,7 @@
       </c>
       <c r="C1061" s="1" t="inlineStr">
         <is>
-          <t>a.saw.ˈta.ɾãʊ̃</t>
+          <t>/a.saw.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1061" s="1" t="inlineStr">
@@ -34474,7 +34582,11 @@
           <t>哎呀&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1068" s="1" t="inlineStr"/>
+      <c r="C1068" s="1" t="inlineStr">
+        <is>
+          <t>/d͡ʒiː/</t>
+        </is>
+      </c>
       <c r="D1068" s="1" t="inlineStr">
         <is>
           <t>哎呀</t>
@@ -34627,7 +34739,7 @@
       </c>
       <c r="B1073" s="1" t="inlineStr">
         <is>
-          <t>[mɐ̃ˈʃa(ʁ)] 失去光泽&lt;动&gt;</t>
+          <t>[mɐ̃ˈʃa(ʁ)] 弄脏；玷污；留下污迹&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1073" s="1" t="inlineStr">
@@ -34637,7 +34749,7 @@
       </c>
       <c r="D1073" s="1" t="inlineStr">
         <is>
-          <t>失去光泽</t>
+          <t>弄脏；玷污；留下污迹</t>
         </is>
       </c>
       <c r="E1073" s="1" t="inlineStr">
@@ -35043,7 +35155,7 @@
       </c>
       <c r="B1086" s="1" t="inlineStr">
         <is>
-          <t>[pi.ɾa.teˈa(ʁ)] 海盗&lt;动&gt;</t>
+          <t>[pi.ɾa.teˈa(ʁ)] 盗版；剽窃；进行海盗劫掠&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1086" s="1" t="inlineStr">
@@ -35053,7 +35165,7 @@
       </c>
       <c r="D1086" s="1" t="inlineStr">
         <is>
-          <t>海盗</t>
+          <t>盗版；剽窃；进行海盗劫掠</t>
         </is>
       </c>
       <c r="E1086" s="1" t="inlineStr">
@@ -35203,17 +35315,17 @@
       </c>
       <c r="B1091" s="1" t="inlineStr">
         <is>
-          <t>[dʒis.tã.ˈsi.ə] 距离&lt;名&gt;</t>
+          <t>[dʒis.tã.ˈsi.ə] 使疏远，拉开距离&lt;动&gt;（distanciar 的第三人称单数现在时）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1091" s="1" t="inlineStr">
         <is>
-          <t>dʒis.tã.ˈsi.ə</t>
+          <t>/dʒis.tã.ˈsi.ə/</t>
         </is>
       </c>
       <c r="D1091" s="1" t="inlineStr">
         <is>
-          <t>距离</t>
+          <t>使疏远，拉开距离&lt;动&gt;（distanciar 的第三人称单数现在时）</t>
         </is>
       </c>
       <c r="E1091" s="1" t="inlineStr">
@@ -35235,7 +35347,7 @@
       </c>
       <c r="B1092" s="1" t="inlineStr">
         <is>
-          <t>[kõ.tɾa.ɾiˈa(ʁ)] 柜台&lt;动&gt;</t>
+          <t>[kõ.tɾa.ɾiˈa(ʁ)] 违背；反对；阻挠；使不快&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1092" s="1" t="inlineStr">
@@ -35245,7 +35357,7 @@
       </c>
       <c r="D1092" s="1" t="inlineStr">
         <is>
-          <t>柜台</t>
+          <t>违背；反对；阻挠；使不快</t>
         </is>
       </c>
       <c r="E1092" s="1" t="inlineStr">
@@ -35334,7 +35446,11 @@
           <t>元首&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1095" s="1" t="inlineStr"/>
+      <c r="C1095" s="1" t="inlineStr">
+        <is>
+          <t>/fu.ˈʁɛʁ/</t>
+        </is>
+      </c>
       <c r="D1095" s="1" t="inlineStr">
         <is>
           <t>元首</t>
